--- a/public/files/VendorPassTemplate.xlsx
+++ b/public/files/VendorPassTemplate.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Passport Number *</t>
+          <t>Passport Number</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">

--- a/public/files/VendorPassTemplate.xlsx
+++ b/public/files/VendorPassTemplate.xlsx
@@ -6820,7 +6820,7 @@
     <dataValidation sqref="D2:D101" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
       <formula1>DropdownList_3</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E101" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
+    <dataValidation sqref="E2:E101" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Location Access" prompt="Pick one from the list, or type several separated by a comma, e.g. KPK Gate, KSB Phase 2 Gate" type="list" errorStyle="stop">
       <formula1>DropdownList_4</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F101" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop">
